--- a/World Cup PlayBook26.xlsx
+++ b/World Cup PlayBook26.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\world-cup-pool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB220B7-1FE9-4E2F-A55C-59A308A701F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{250A2305-9C37-4ACB-B18E-5465F38A8EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1185" yWindow="1515" windowWidth="25560" windowHeight="29685" xr2:uid="{6A19B9C8-EC2E-4053-BDD7-1696BB2AA53D}"/>
   </bookViews>
@@ -565,9 +565,6 @@
     <t>Mert Günok</t>
   </si>
   <si>
-    <t>Dayne St. Clair</t>
-  </si>
-  <si>
     <t>Sergio Rochet</t>
   </si>
   <si>
@@ -731,6 +728,9 @@
   </si>
   <si>
     <t>João Neves</t>
+  </si>
+  <si>
+    <t>Maxime Crépeau</t>
   </si>
 </sst>
 </file>
@@ -843,7 +843,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -969,12 +969,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1097,6 +1106,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1531,7 +1541,7 @@
     <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="18"/>
       <c r="B5" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>60</v>
@@ -1618,7 +1628,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>15</v>
@@ -1654,7 +1664,7 @@
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>7</v>
@@ -1664,7 +1674,7 @@
         <v>69</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>53</v>
@@ -1713,7 +1723,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>103</v>
@@ -1728,14 +1738,14 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="18"/>
       <c r="B12" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>14</v>
@@ -1816,7 +1826,7 @@
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F15" s="26" t="s">
         <v>60</v>
@@ -1866,7 +1876,7 @@
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
       <c r="K17" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -1901,17 +1911,17 @@
     <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="18"/>
       <c r="B19" s="21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>103</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G19" s="20"/>
       <c r="H19" s="12" t="s">
@@ -1947,13 +1957,13 @@
         <v>60</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>
       <c r="B21" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>19</v>
@@ -1967,13 +1977,13 @@
       </c>
       <c r="G21" s="20"/>
       <c r="H21" s="27" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>37</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -1986,7 +1996,7 @@
       </c>
       <c r="D22" s="20"/>
       <c r="E22" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>11</v>
@@ -2085,10 +2095,10 @@
       </c>
       <c r="G26" s="20"/>
       <c r="H26" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I26" s="22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -2131,7 +2141,7 @@
       </c>
       <c r="G28" s="20"/>
       <c r="H28" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I28" s="13" t="s">
         <v>2</v>
@@ -2140,7 +2150,7 @@
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="18"/>
       <c r="B29" s="29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>60</v>
@@ -2282,7 +2292,7 @@
       </c>
       <c r="G34" s="20"/>
       <c r="H34" s="23" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I34" s="29" t="s">
         <v>64</v>
@@ -2302,7 +2312,7 @@
       </c>
       <c r="D35" s="20"/>
       <c r="E35" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F35" s="22" t="s">
         <v>123</v>
@@ -2356,7 +2366,7 @@
       </c>
       <c r="D37" s="20"/>
       <c r="E37" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F37" s="19" t="s">
         <v>62</v>
@@ -2366,7 +2376,7 @@
         <v>109</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L37" s="6">
         <v>8</v>
@@ -2402,10 +2412,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="F39" s="22" t="s">
         <v>207</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>208</v>
       </c>
       <c r="G39" s="20">
         <v>18</v>
@@ -2438,7 +2448,7 @@
       </c>
       <c r="G40" s="20"/>
       <c r="H40" s="37" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I40" s="30" t="s">
         <v>12</v>
@@ -2458,14 +2468,14 @@
       </c>
       <c r="D41" s="20"/>
       <c r="E41" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F41" s="19" t="s">
         <v>36</v>
       </c>
       <c r="G41" s="20"/>
       <c r="H41" s="31" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I41" s="32" t="s">
         <v>19</v>
@@ -2488,14 +2498,14 @@
         <v>112</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G42" s="20"/>
       <c r="H42" s="13" t="s">
         <v>131</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L42" s="6">
         <v>13</v>
@@ -2508,11 +2518,11 @@
         <v>153</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D43" s="20"/>
       <c r="E43" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F43" s="19" t="s">
         <v>34</v>
@@ -2535,7 +2545,7 @@
         <v>155</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D44" s="20"/>
       <c r="E44" s="12" t="s">
@@ -2648,7 +2658,7 @@
       </c>
       <c r="G48" s="20"/>
       <c r="H48" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I48" s="12" t="s">
         <v>11</v>
@@ -2661,7 +2671,7 @@
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="18"/>
       <c r="B49" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C49" s="19" t="s">
         <v>12</v>
@@ -2695,14 +2705,14 @@
       </c>
       <c r="D50" s="20"/>
       <c r="E50" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F50" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G50" s="20"/>
       <c r="H50" s="28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I50" s="19" t="s">
         <v>64</v>
@@ -2725,11 +2735,11 @@
         <v>166</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G51" s="20"/>
       <c r="H51" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>2</v>
@@ -2777,7 +2787,7 @@
         <v>24</v>
       </c>
       <c r="H53" s="41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I53" s="40" t="s">
         <v>11</v>
@@ -2817,7 +2827,7 @@
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="18"/>
       <c r="B55" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>19</v>
@@ -2858,7 +2868,7 @@
       </c>
       <c r="G56" s="20"/>
       <c r="H56" s="46" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I56" s="43" t="s">
         <v>14</v>
@@ -2871,21 +2881,21 @@
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="18"/>
       <c r="B57" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C57" s="19" t="s">
         <v>88</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F57" s="43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G57" s="20"/>
       <c r="H57" s="46" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I57" s="43" t="s">
         <v>76</v>
@@ -2894,7 +2904,7 @@
     <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="18"/>
       <c r="B58" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>15</v>
@@ -2964,10 +2974,10 @@
       </c>
       <c r="D61" s="20"/>
       <c r="E61" s="46" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F61" s="51" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G61" s="20"/>
       <c r="H61" s="45" t="s">
@@ -2993,8 +3003,8 @@
         <v>37</v>
       </c>
       <c r="G62" s="20"/>
-      <c r="H62" s="45" t="s">
-        <v>179</v>
+      <c r="H62" s="54" t="s">
+        <v>234</v>
       </c>
       <c r="I62" s="43" t="s">
         <v>73</v>
@@ -3003,21 +3013,21 @@
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C63" s="43" t="s">
         <v>71</v>
       </c>
       <c r="D63" s="20"/>
       <c r="E63" s="42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F63" s="43" t="s">
         <v>62</v>
       </c>
       <c r="G63" s="20"/>
       <c r="H63" s="45" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I63" s="43" t="s">
         <v>84</v>
@@ -3026,21 +3036,21 @@
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="44" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C64" s="43" t="s">
         <v>79</v>
       </c>
       <c r="D64" s="20"/>
       <c r="E64" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F64" s="43" t="s">
         <v>93</v>
       </c>
       <c r="G64" s="20"/>
       <c r="H64" s="44" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I64" s="43" t="s">
         <v>100</v>
@@ -3056,14 +3066,14 @@
       </c>
       <c r="D65" s="20"/>
       <c r="E65" s="53" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F65" s="48" t="s">
         <v>81</v>
       </c>
       <c r="G65" s="20"/>
       <c r="H65" s="47" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I65" s="48" t="s">
         <v>114</v>
@@ -3081,13 +3091,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E68" s="4"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E69" s="3"/>
     </row>
